--- a/datasets/day1_excel_foundations/03_worksheets_and_navigation/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/03_worksheets_and_navigation/practice_start.xlsx
@@ -455,7 +455,7 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
     <col width="22.5" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="10.5" customWidth="1" min="6" max="6"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
